--- a/FINAL - checklist hardening measures.xlsx
+++ b/FINAL - checklist hardening measures.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilya\Desktop\Project 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B903FBFF-54B1-42D4-A858-525D5BEF74FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D99E38-2738-4AA7-9DC0-0054E9D07DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31368" yWindow="0" windowWidth="19488" windowHeight="16656" activeTab="1" xr2:uid="{F240A798-A802-42DC-9264-DF07F3B73030}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{F240A798-A802-42DC-9264-DF07F3B73030}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="78">
   <si>
     <t>Double check security</t>
   </si>
@@ -270,24 +270,6 @@
     <t>2811 VOIP VOICE</t>
   </si>
   <si>
-    <t>bad password</t>
-  </si>
-  <si>
-    <t>disabled?</t>
-  </si>
-  <si>
-    <t>maybe?</t>
-  </si>
-  <si>
-    <t>check password</t>
-  </si>
-  <si>
-    <t>login auth default?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lines vty 0 4 secured, lines 5 through 14 not secured </t>
-  </si>
-  <si>
     <t>should work</t>
   </si>
   <si>
@@ -297,10 +279,25 @@
     <t>login console access</t>
   </si>
   <si>
-    <t xml:space="preserve">discussion: do we want a guess wifi ? </t>
-  </si>
-  <si>
     <t>Switches</t>
+  </si>
+  <si>
+    <t>cisco123</t>
+  </si>
+  <si>
+    <t>cisco</t>
+  </si>
+  <si>
+    <t>(config)#line vty 0 14
+(config-line)#transport input ssh
+exit
+exit
+#copy running-config startup-config</t>
+  </si>
+  <si>
+    <t>(config)#line vty 0 14
+password … 
+login</t>
   </si>
 </sst>
 </file>
@@ -339,7 +336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -366,13 +363,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -402,12 +393,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,19 +836,19 @@
       <c r="G7" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -870,10 +866,10 @@
       <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="9"/>
       <c r="J8" t="s">
         <v>4</v>
       </c>
@@ -1191,8 +1187,6 @@
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
       <c r="D19" t="s">
         <v>67</v>
       </c>
@@ -1225,8 +1219,6 @@
       <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
       <c r="D21" t="s">
         <v>67</v>
       </c>
@@ -1241,8 +1233,6 @@
       <c r="A22" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
       <c r="D22" t="s">
         <v>67</v>
       </c>
@@ -1415,27 +1405,26 @@
     <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="15.21875" customWidth="1"/>
     <col min="7" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" customWidth="1"/>
-    <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>31</v>
       </c>
@@ -1454,19 +1443,18 @@
       <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="J7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D8" t="s">
@@ -1487,41 +1475,37 @@
       <c r="I8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" t="s">
+      <c r="J8" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L8" t="s">
+      <c r="K8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M8" t="s">
+      <c r="L8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M8" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="N8" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="O8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P8" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="P8" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="I9" t="s">
         <v>53</v>
       </c>
-      <c r="J9" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="O9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1529,7 +1513,7 @@
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>48</v>
@@ -1547,7 +1531,7 @@
         <v>48</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
         <v>48</v>
@@ -1567,11 +1551,8 @@
       <c r="P10" t="s">
         <v>48</v>
       </c>
-      <c r="Q10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1580,49 +1561,46 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="I11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" t="s">
+        <v>48</v>
+      </c>
+      <c r="O11" t="s">
+        <v>67</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1630,52 +1608,52 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
+      <c r="B13" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
@@ -1691,32 +1669,29 @@
       <c r="H13" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1731,7 +1706,7 @@
         <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
         <v>48</v>
@@ -1739,35 +1714,32 @@
       <c r="H14" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" t="s">
+        <v>48</v>
+      </c>
+      <c r="O14" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1781,7 +1753,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
         <v>48</v>
@@ -1789,90 +1761,84 @@
       <c r="H15" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" t="s">
+        <v>48</v>
+      </c>
+      <c r="O15" t="s">
+        <v>48</v>
+      </c>
+      <c r="P15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="6"/>
       <c r="D16" t="s">
         <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="6" t="s">
+      <c r="F16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
         <v>67</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="11" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="2"/>
@@ -1880,96 +1846,90 @@
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" t="s">
+        <v>35</v>
+      </c>
+      <c r="P17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>62</v>
+      <c r="B18" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
         <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
         <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" t="s">
+        <v>48</v>
+      </c>
+      <c r="N18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1986,263 +1946,261 @@
         <v>48</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19" t="s">
+        <v>48</v>
+      </c>
+      <c r="O19" t="s">
+        <v>48</v>
+      </c>
+      <c r="P19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
       <c r="D20" t="s">
         <v>35</v>
       </c>
       <c r="E20" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="F20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" t="s">
         <v>67</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="6"/>
       <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="6" t="s">
+      <c r="E21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" t="s">
         <v>67</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
       <c r="D22" t="s">
         <v>35</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="6" t="s">
+      <c r="F22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" t="s">
         <v>67</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
       <c r="D23" t="s">
         <v>35</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" s="6" t="s">
+      <c r="F23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
         <v>67</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L24" t="s">
-        <v>48</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -2252,77 +2210,82 @@
       <c r="E25" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" t="s">
         <v>48</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="I26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J26" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2333,60 +2296,53 @@
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
         <v>35</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" s="6" t="s">
+      <c r="G27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
         <v>67</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -2405,35 +2361,32 @@
       <c r="H30" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>67</v>
+      <c r="I30" t="s">
+        <v>67</v>
+      </c>
+      <c r="J30" t="s">
+        <v>35</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="L30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="P30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q30" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2444,88 +2397,82 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" t="s">
         <v>48</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q31" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="L31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" t="s">
         <v>67</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="P32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P32" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2534,74 +2481,64 @@
         <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
         <v>35</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>35</v>
+        <v>48</v>
+      </c>
+      <c r="I33" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" t="s">
+        <v>48</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="O33" t="s">
         <v>35</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Q33" s="7" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="J35" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>75</v>
-      </c>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -2615,12 +2552,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:Q7"/>
-    <mergeCell ref="I8:J8"/>
+  <mergeCells count="1">
+    <mergeCell ref="J7:P7"/>
   </mergeCells>
-  <conditionalFormatting sqref="D10:Q34">
+  <conditionalFormatting sqref="D10:P34">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>" "</formula>
     </cfRule>
